--- a/output/pdf_financials_xlsx/RVLY.xlsx
+++ b/output/pdf_financials_xlsx/RVLY.xlsx
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.184651</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.156363</v>
       </c>
     </row>
     <row r="125">
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.184651</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.156363</v>
       </c>
     </row>
     <row r="126">
@@ -6372,7 +6372,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RVLY.xlsx
+++ b/output/pdf_financials_xlsx/RVLY.xlsx
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-23.796497</v>
+        <v>-22.701641</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-22.410243</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.094856</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-23.796497</v>
+        <v>-22.701641</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-22.410243</v>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-23.513112</v>
+        <v>-22.418256</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-22.145805</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-144.8061265022956</v>
+        <v>-138.0634266658045</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-163.4318978687026</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.822805540797689</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -7553,7 +7553,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
